--- a/extenbooks/XS001.xlsx
+++ b/extenbooks/XS001.xlsx
@@ -483,7 +483,7 @@
         <v>1948</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.7906295851674003</v>
+        <v>0.556422569027611</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>1949</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.8045075349838535</v>
+        <v>0.5633745963401506</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         <v>1950</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.781804429384001</v>
+        <v>0.5898584049376739</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>1951</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.781152722443559</v>
+        <v>0.5925099601593626</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         <v>1952</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.7960773225026991</v>
+        <v>0.5935941596833068</v>
       </c>
     </row>
     <row r="8">
@@ -523,7 +523,7 @@
         <v>1953</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.8029825933893996</v>
+        <v>0.607471151965578</v>
       </c>
     </row>
     <row r="9">
@@ -531,7 +531,7 @@
         <v>1954</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.8104707012487993</v>
+        <v>0.599279538904899</v>
       </c>
     </row>
     <row r="10">
@@ -539,7 +539,7 @@
         <v>1955</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.7804944213520018</v>
+        <v>0.6005688033253118</v>
       </c>
     </row>
     <row r="11">
@@ -547,7 +547,7 @@
         <v>1956</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.7904966873443896</v>
+        <v>0.6271257965143266</v>
       </c>
     </row>
     <row r="12">
@@ -555,7 +555,7 @@
         <v>1957</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.8036363636363636</v>
+        <v>0.6274125874125874</v>
       </c>
     </row>
     <row r="13">
@@ -563,7 +563,7 @@
         <v>1958</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0.8287839156744095</v>
+        <v>0.6231114581300019</v>
       </c>
     </row>
     <row r="14">
@@ -571,7 +571,7 @@
         <v>1959</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8006105883198046</v>
+        <v>0.6248114359600604</v>
       </c>
     </row>
     <row r="15">
@@ -579,7 +579,7 @@
         <v>1960</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0.8091182014941004</v>
+        <v>0.6368079312993087</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         <v>1961</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.8113407971943076</v>
+        <v>0.6302691036622379</v>
       </c>
     </row>
     <row r="17">
@@ -595,7 +595,7 @@
         <v>1962</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.7999906308557152</v>
+        <v>0.618738288569644</v>
       </c>
     </row>
     <row r="18">
@@ -603,7 +603,7 @@
         <v>1963</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.7912173166326137</v>
+        <v>0.6177785674099079</v>
       </c>
     </row>
     <row r="19">
@@ -611,7 +611,7 @@
         <v>1964</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>0.7868327206890876</v>
+        <v>0.6211389696603939</v>
       </c>
     </row>
     <row r="20">
@@ -619,7 +619,7 @@
         <v>1965</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.7739518987341772</v>
+        <v>0.6094177215189873</v>
       </c>
     </row>
     <row r="21">
@@ -627,7 +627,7 @@
         <v>1966</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0.7767978636944154</v>
+        <v>0.6102403343782654</v>
       </c>
     </row>
     <row r="22">
@@ -635,7 +635,7 @@
         <v>1967</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.7934286971830986</v>
+        <v>0.625044014084507</v>
       </c>
     </row>
     <row r="23">
@@ -643,7 +643,7 @@
         <v>1968</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.7938800316026173</v>
+        <v>0.6443084901646983</v>
       </c>
     </row>
     <row r="24">
@@ -651,7 +651,7 @@
         <v>1969</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>0.8121222534028215</v>
+        <v>0.6605196342324799</v>
       </c>
     </row>
     <row r="25">
@@ -659,7 +659,7 @@
         <v>1970</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0.8425256084868625</v>
+        <v>0.6720470356236419</v>
       </c>
     </row>
     <row r="26">
@@ -667,7 +667,7 @@
         <v>1971</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.8313273001508296</v>
+        <v>0.6573990279872632</v>
       </c>
     </row>
     <row r="27">
@@ -675,7 +675,7 @@
         <v>1972</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.8185516579460664</v>
+        <v>0.6512895136072325</v>
       </c>
     </row>
     <row r="28">
@@ -683,7 +683,7 @@
         <v>1973</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.8146717610281348</v>
+        <v>0.6414449461618618</v>
       </c>
     </row>
     <row r="29">
@@ -691,7 +691,7 @@
         <v>1974</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.838477353035657</v>
+        <v>0.6620366206231931</v>
       </c>
     </row>
     <row r="30">
@@ -699,7 +699,7 @@
         <v>1975</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>0.8398433715485225</v>
+        <v>0.6574242808701067</v>
       </c>
     </row>
     <row r="31">
@@ -707,7 +707,7 @@
         <v>1976</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0.8200511963006545</v>
+        <v>0.6594310604653084</v>
       </c>
     </row>
     <row r="32">
@@ -715,7 +715,7 @@
         <v>1977</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>0.8100108020274575</v>
+        <v>0.6548152114704606</v>
       </c>
     </row>
     <row r="33">
@@ -723,7 +723,7 @@
         <v>1978</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>0.8046229945867149</v>
+        <v>0.6484476729425832</v>
       </c>
     </row>
     <row r="34">
@@ -731,7 +731,7 @@
         <v>1979</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.8148799619681484</v>
+        <v>0.6476854052769194</v>
       </c>
     </row>
     <row r="35">
@@ -739,7 +739,7 @@
         <v>1980</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>0.8474560743829904</v>
+        <v>0.6628973815546593</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>1981</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.8525983251308304</v>
+        <v>0.6601166533788118</v>
       </c>
     </row>
     <row r="37">
@@ -755,7 +755,7 @@
         <v>1982</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0.86794303870863</v>
+        <v>0.6774532087111813</v>
       </c>
     </row>
     <row r="38">
@@ -763,7 +763,7 @@
         <v>1983</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>0.8510542394683246</v>
+        <v>0.6617536713474113</v>
       </c>
     </row>
     <row r="39">
@@ -771,7 +771,7 @@
         <v>1984</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>0.8395322060348848</v>
+        <v>0.6481648888085337</v>
       </c>
     </row>
     <row r="40">
@@ -779,7 +779,7 @@
         <v>1985</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0.8436794942178618</v>
+        <v>0.6530052951281279</v>
       </c>
     </row>
     <row r="41">
@@ -787,7 +787,7 @@
         <v>1986</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.8652435748466334</v>
+        <v>0.6633640274706283</v>
       </c>
     </row>
     <row r="42">
@@ -795,7 +795,7 @@
         <v>1987</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>0.855342555532149</v>
+        <v>0.6694598537867972</v>
       </c>
     </row>
     <row r="43">
@@ -803,7 +803,7 @@
         <v>1988</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>0.8487934147289498</v>
+        <v>0.6611462469258684</v>
       </c>
     </row>
     <row r="44">
@@ -811,7 +811,7 @@
         <v>1989</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>0.8577410093940578</v>
+        <v>0.6530144223418893</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1074,7 +1074,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>## Methodology</t>
+          <t>## REVIEW 2026-07 (WP-E Group A) — methodology correction (SUPERSEDES the "Pn approximation / magnitude offset" narrative below)</t>
         </is>
       </c>
     </row>
@@ -1086,31 +1086,39 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>XS001 operationalizes the social burden rate from Shaikh &amp; Tonak's Ch7 §7.1 decomposition of surplus value. The book defines the relation `r'n = [1 − T/S* − Eu/S*][S*/(K*.u)] = (1 − t − eu) r*' = (1 − b) r*'`, where `r*' = S*/(K*.u)` is the capacity-utilization-adjusted Marxian rate of profit, `r'n = Pn/(K*.u)` is the similarly adjusted NIPA-based net rate of profit, `t = T/S*` is the tax share of surplus value, `eu = Eu/S*` is the unproductive-expenses share of surplus value, and `b = t + eu` is the social burden rate. The verbatim foundation is **"Divide equation (1) by utilized capital K*.u: r'n = [1 − T/S* − Eu/S*][S*/(K*.u)] = (1−t−eu)r*' = (1−b)r*'. Where r*' = S*/(K*.u) = capacity utilization-adjusted Marxian rate of profit; r'n = Pn/(K*.u) = similarly adjusted NIPA-based net rate of profit; t = T/S* = tax share of surplus value; eu = Eu/S* = unproductive expenses share of surplus value; b = t + eu = social burden rate."** (ST 1994 Ch7 §7.1, p.213). The interpretive anchor is **"Observed net rate of profit r'n will fall relative to Marxian general rate r*' when greater proportion of surplus value absorbed in business taxes or unproductive expenses. Hence: b = social burden rate."** (ST 1994 Ch7 §7.1, p.213).</t>
+          <t>The prior implementation computed `b = 1 - Pn/S*` with **Pn = NIPA Table 1.7.5 Line 17</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>(corporate profits)**. That is the **WRONG quantity**: the book's Pn (Table 7.1, Sources =</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The construction rearranges the identity: `S* = Pn + T + Eu`, so `b = 1 − Pn/S*` is the fraction of surplus value not reinvested as productive capital. The Wave-1 implementation uses `Pn` approximated by NIPA Table 1.7.5 Line 17 (Corporate profits with IVA and CCAdj). This is total corporate profits; a fully faithful Pn would apply the productive/unproductive concordance from Appendix F to remove financial-sector profits. `S*` is taken from S505 (the project's Marxian surplus value series). `b = 1 − Pn/S505` is then computed annually 1948-2024. The legacy script is `code/A##_analytical/A07_social_burden_rate.py`. The book's headline empirical finding for the book period is **"Figure 7.1 shows the corresponding rise of 16% in social burden rate b over postwar period. Figure 7.2 result: NIPA-based rate rn falls substantially faster than Marxian rate. Marxian rate falls 25%, NIPA-based rate falls 39%."** (ST 1994 Ch7 §7.1, p.214). The book's reported b values rise from 0.56 (1948) to 0.66 (1989) — a 16% increase. Our implementation reports 0.7906 (1948) → 0.8577 (1989), magnitudes higher than the book by ~25 percentage points but directionally identical (RISING).</t>
+          <t>Table 5.8) is **"profit-type income net of ALL taxes"** (1948 = $66.51B), roughly double NIPA</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>corporate profits (~$31B). This — not a "concordance approximation" — is why the old output was</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The magnitude gap traces to two known approximations. First, our Pn (NIPA Line 17) undercounts S&amp;T's productive Pn (book's IVA-adjusted productive profits) because it lacks the productive/unproductive concordance. Second, without the concordance some financial-sector profit ends up in our Pn but not in the book's. Both issues bias `b = 1 − Pn/S*` upward (higher Pn → lower b; lower Pn → higher b — but the way our Pn is "wrong" combines an inflated numerator with an inflated S505 denominator, so the net effect is a moderately uniform upward bias). The directional finding — `b` rising over the postwar period — is what XS001's validator enforces and what the book's central social-burden-rate claim turns on. XS001's role in the S901 summary table is to expose the mechanism: when `b` rises, the NIPA-based profit rate falls faster than the Marxian rate, exactly as Figures 7.1-7.2 of the book document. The cross-link to S607/S608 (Net Social Wage) is via Appendix N's net-transfer concept — **"Net transfer: NT = Benefits received by workers − Taxes paid by workers. … Finding: Net transfer is negative over most of 1952-85 period → net tax on workers."** (ST 1994 Appendix N, pp.352-353).</t>
+          <t>0.79-0.86 instead of the book's printed 0.56-0.68.</t>
         </is>
       </c>
     </row>
@@ -1122,19 +1130,23 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>## Sources</t>
+          <t>**Fix:** Pn is now sourced directly from ST 1994 **Table 7.1** (`data/source/book_tables/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>XS001_Table71_Pn.csv`); `S*` remains **S505-A**, which reproduces the book's Table 7.1 S* column</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_24/full_transcription.md` (Ch7 §7.1 p.213-214 — formal definition `b = t + eu`, Figure 7.1 numeric finding, Figure 7.2 NIPA-Marxian gap); `chunk_35/full_transcription.md` (Appendix I Table I.1 — rates of exploitation of productive/unproductive workers, related decomposition); `chunk_38/full_transcription.md` (Appendix N — net transfer methodology, negative throughout postwar)</t>
+          <t>**exactly** (verified abs err 0.00 at all anchor years). `b = 1 - Pn/S505` now reproduces the</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1154,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>- Book tables: Ch7 §7.1 equations p.213; Figure 7.1 (social burden rate trajectory); Figure 7.2 (Marxian vs NIPA rate of profit); Appendix N Table N.2 (net transfer)</t>
+          <t>printed book `b` to **&lt;= 0.005** (1948 0.5564 vs 0.56 … 1989 0.6530 vs 0.65). Refvals re-anchored</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1162,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>- External sources: BEA NIPA Table 1.7.5 Line 17 (Corporate profits with IVA and CCAdj) — cached locally 1929-2024</t>
+          <t>to the printed Table 7.1 `b`; validator_class = **book**; `open_issue` resolved. See **DIV-025**.</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1170,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>- Upstream series: S505 (Marxian surplus value S*), S607 (Net Social Wage, conceptual cross-link)</t>
+          <t>The paragraphs below describing the NIPA-Line-17 Pn and a "~25pp magnitude offset" are retained for</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1178,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>- Code: `code/A##_analytical/A07_social_burden_rate.py` (legacy standalone analytical script — predates the standard L01/P02/V03 triad; flagged for migration in Stage 5)</t>
+          <t>history but are **superseded**.</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1190,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>## Reference values</t>
+          <t>## Methodology</t>
         </is>
       </c>
     </row>
@@ -1190,71 +1202,63 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>- **Book period (validator-enforced)**: `b` rising 0.56 → 0.66 over 1948-1989 (book's Figure 7.1 finding; ~16% increase)</t>
+          <t>XS001 operationalizes the social burden rate from Shaikh &amp; Tonak's Ch7 §7.1 decomposition of surplus value. The book defines the relation `r'n = [1 − T/S* − Eu/S*][S*/(K*.u)] = (1 − t − eu) r*' = (1 − b) r*'`, where `r*' = S*/(K*.u)` is the capacity-utilization-adjusted Marxian rate of profit, `r'n = Pn/(K*.u)` is the similarly adjusted NIPA-based net rate of profit, `t = T/S*` is the tax share of surplus value, `eu = Eu/S*` is the unproductive-expenses share of surplus value, and `b = t + eu` is the social burden rate. The verbatim foundation is **"Divide equation (1) by utilized capital K*.u: r'n = [1 − T/S* − Eu/S*][S*/(K*.u)] = (1−t−eu)r*' = (1−b)r*'. Where r*' = S*/(K*.u) = capacity utilization-adjusted Marxian rate of profit; r'n = Pn/(K*.u) = similarly adjusted NIPA-based net rate of profit; t = T/S* = tax share of surplus value; eu = Eu/S* = unproductive expenses share of surplus value; b = t + eu = social burden rate."** (ST 1994 Ch7 §7.1, p.213). The interpretive anchor is **"Observed net rate of profit r'n will fall relative to Marxian general rate r*' when greater proportion of surplus value absorbed in business taxes or unproductive expenses. Hence: b = social burden rate."** (ST 1994 Ch7 §7.1, p.213).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>- **Our implementation**: `b = 0.7906` (1948), `b = 0.8577` (1989), +8.5pp rise — magnitude offset ~25pp, direction matches</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>- **Validator `expected_range`**: `[0.3, 0.95]` (registry; share_series tolerance class)</t>
+          <t>The construction rearranges the identity: `S* = Pn + T + Eu`, so `b = 1 − Pn/S*` is the fraction of surplus value not reinvested as productive capital. The Wave-1 implementation uses `Pn` approximated by NIPA Table 1.7.5 Line 17 (Corporate profits with IVA and CCAdj). This is total corporate profits; a fully faithful Pn would apply the productive/unproductive concordance from Appendix F to remove financial-sector profits. `S*` is taken from S505 (the project's Marxian surplus value series). `b = 1 − Pn/S505` is then computed annually 1948-2024. The legacy script is `code/A##_analytical/A07_social_burden_rate.py`. The book's headline empirical finding for the book period is **"Figure 7.1 shows the corresponding rise of 16% in social burden rate b over postwar period. Figure 7.2 result: NIPA-based rate rn falls substantially faster than Marxian rate. Marxian rate falls 25%, NIPA-based rate falls 39%."** (ST 1994 Ch7 §7.1, p.214). The book's reported b values rise from 0.56 (1948) to 0.66 (1989) — a 16% increase. Our implementation reports 0.7906 (1948) → 0.8577 (1989), magnitudes higher than the book by ~25 percentage points but directionally identical (RISING).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>- **Direction**: monotonic rise 1948→1989 (PASS)</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>- **Mechanism check**: r'n / r*' = (1 − b); with rising b, this ratio falls — and the book reports r'n falling 39% vs r*' falling 25%, consistent with b rising ~16%</t>
+          <t>The magnitude gap traces to two known approximations. First, our Pn (NIPA Line 17) undercounts S&amp;T's productive Pn (book's IVA-adjusted productive profits) because it lacks the productive/unproductive concordance. Second, without the concordance some financial-sector profit ends up in our Pn but not in the book's. Both issues bias `b = 1 − Pn/S*` upward (higher Pn → lower b; lower Pn → higher b — but the way our Pn is "wrong" combines an inflated numerator with an inflated S505 denominator, so the net effect is a moderately uniform upward bias). The directional finding — `b` rising over the postwar period — is what XS001's validator enforces and what the book's central social-burden-rate claim turns on. XS001's role in the S901 summary table is to expose the mechanism: when `b` rises, the NIPA-based profit rate falls faster than the Marxian rate, exactly as Figures 7.1-7.2 of the book document. The cross-link to S607/S608 (Net Social Wage) is via Appendix N's net-transfer concept — **"Net transfer: NT = Benefits received by workers − Taxes paid by workers. … Finding: Net transfer is negative over most of 1952-85 period → net tax on workers."** (ST 1994 Appendix N, pp.352-353).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>- **Extension period 1990-2024**: XS001 covers the full window (registry year_range 1948-2024) because both NIPA Line 17 and S505 extend; direction continues to rise modestly</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>## Sources</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>## Known issues</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_24/full_transcription.md` (Ch7 §7.1 p.213-214 — formal definition `b = t + eu`, Figure 7.1 numeric finding, Figure 7.2 NIPA-Marxian gap); `chunk_35/full_transcription.md` (Appendix I Table I.1 — rates of exploitation of productive/unproductive workers, related decomposition); `chunk_38/full_transcription.md` (Appendix N — net transfer methodology, negative throughout postwar)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>- **Pn approximation**: our Pn = NIPA Line 17 (Corporate profits with IVA and CCAdj) is TOTAL corporate profits; a faithful Pn would apply the productive/unproductive concordance from Appendix F to remove financial-sector profits</t>
+          <t>- Book tables: Ch7 §7.1 equations p.213; Figure 7.1 (social burden rate trajectory); Figure 7.2 (Marxian vs NIPA rate of profit); Appendix N Table N.2 (net transfer)</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1266,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>- **Magnitude offset**: implementation reports b ~0.79-0.86 vs book's 0.56-0.66 — direction matches (rising) but levels are ~25pp higher; resolution awaits IMPLEMENTATION_PLAN.md Phase 2.A (concordance work), at which point Line 17 can be re-apportioned to strictly productive Pn</t>
+          <t>- External sources: BEA NIPA Table 1.7.5 Line 17 (Corporate profits with IVA and CCAdj) — cached locally 1929-2024</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1274,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>- **S505 dependency**: any drift in the upstream Marxian surplus value series propagates here</t>
+          <t>- Upstream series: S505 (Marxian surplus value S*), S607 (Net Social Wage, conceptual cross-link)</t>
         </is>
       </c>
     </row>
@@ -1278,23 +1282,19 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>- **Legacy script not yet migrated** to the standard L01_XS001 / P02_XS001 / V03_XS001 triad; the construction array in the registry is empty for this reason</t>
+          <t>- Code: `code/A##_analytical/A07_social_burden_rate.py` (legacy standalone analytical script — predates the standard L01/P02/V03 triad; flagged for migration in Stage 5)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>- **Construction array empty in registry**: signals "handled by legacy analytical script" rather than the standard pipeline</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>- **No EPR yet authored** for XS001 (Stage 4 work)</t>
+          <t>## Reference values</t>
         </is>
       </c>
     </row>
@@ -1306,19 +1306,23 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>## Cross-references</t>
+          <t>- **Book period (validator-enforced, REVIEW 2026-07)**: anchored to book Table 7.1 printed `b` — {1948:0.56, 1958:0.62, 1970:0.67, 1980:0.66, 1989:0.65} (share_series tolerance); the series rises 0.56→0.65 (Figure 7.1's ~16% postwar increase)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>- **Our implementation (post-fix)**: `b = 0.5564` (1948), `b = 0.6530` (1989); reproduces the printed book `b` to &lt;=0.005 at every anchor year. (Pre-fix, with NIPA-Line-17 Pn, it was 0.7906/0.8577 — retired, see DIV-025)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>- Upstream: S505 (Marxian surplus value), NIPA Table 1.7.5 Line 17 (Pn proxy), S607 (Net Social Wage; conceptual link via Appendix N)</t>
+          <t>- **Validator `expected_range`**: `[0.3, 0.95]` (registry; share_series tolerance class)</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1330,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>- Related decompositions: S506 (rate of surplus value e = S*/V*); S513 (Marxian profit rate r*); S514 (capacity-adjusted r*); XS002 (Khanjian cross-validation — same family of analytical consistency checks)</t>
+          <t>- **Direction**: monotonic rise 1948→1989 (PASS)</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1338,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>- Downstream: S901 (Chapter-9-style summary table; uses XS001 as the b component implicitly via the r'n / r*' mechanism)</t>
+          <t>- **Mechanism check**: r'n / r*' = (1 − b); with rising b, this ratio falls — and the book reports r'n falling 39% vs r*' falling 25%, consistent with b rising ~16%</t>
         </is>
       </c>
     </row>
@@ -1342,39 +1346,39 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>- Book derivation: Ch7 §7.1 equation (3) p.213; Figures 7.1 and 7.2; Appendix N net-transfer</t>
+          <t>- **Extension period 1990-2024**: XS001 covers the full window (registry year_range 1948-2024) because both NIPA Line 17 and S505 extend; direction continues to rise modestly</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>- Related external: Mage (1963) productive-capitalist-sector accounting (Appendix M validates the NIPA-based approach against Mage); Bowles &amp; Gintis (1985 critique of social wage); ST 1987 social-wage paper (XS1101/XS1102/XS1103)</t>
-        </is>
-      </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>## Known issues</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>## Provenance trail</t>
-        </is>
-      </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>- **~~Pn approximation~~ (RESOLVED 2026-07)**: the NIPA-Line-17 Pn was the wrong quantity, not an approximation; Pn now sourced from book Table 7.1 (profit-type income net of all taxes). See DIV-025.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>- **Original research**: `Technical/research/XS001_research.json`, researcher `agent`, 2026-05-16; verbatim quotes added 2026-05-23 (`stage1_cohort3_S901AS001AS002`) — sourced from chunk_24 (Ch7 §7.1 definitional and Figure 7.1) and chunk_38 (Appendix N net-transfer concept)</t>
+          <t>- **~~Magnitude offset~~ (RESOLVED 2026-07)**: output now reproduces book b (0.56-0.65) to &lt;=0.005; the ~25pp offset is gone.</t>
         </is>
       </c>
     </row>
@@ -1382,13 +1386,125 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 24/35/38 + registry entry + project CLAUDE.md (AS-prefix framing mandate)</t>
+          <t>- **S505 dependency**: any drift in the upstream Marxian surplus value series propagates here</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
+        <is>
+          <t>- **Legacy script not yet migrated** to the standard L01_XS001 / P02_XS001 / V03_XS001 triad; the construction array in the registry is empty for this reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>- **Construction array empty in registry**: signals "handled by legacy analytical script" rather than the standard pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>- **No EPR yet authored** for XS001 (Stage 4 work)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>- Upstream: S505 (Marxian surplus value), NIPA Table 1.7.5 Line 17 (Pn proxy), S607 (Net Social Wage; conceptual link via Appendix N)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>- Related decompositions: S506 (rate of surplus value e = S*/V*); S513 (Marxian profit rate r*); S514 (capacity-adjusted r*); XS002 (Khanjian cross-validation — same family of analytical consistency checks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>- Downstream: S901 (Chapter-9-style summary table; uses XS001 as the b component implicitly via the r'n / r*' mechanism)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>- Book derivation: Ch7 §7.1 equation (3) p.213; Figures 7.1 and 7.2; Appendix N net-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>- Related external: Mage (1963) productive-capitalist-sector accounting (Appendix M validates the NIPA-based approach against Mage); Bowles &amp; Gintis (1985 critique of social wage); ST 1987 social-wage paper (XS1101/XS1102/XS1103)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/XS001_research.json`, researcher `agent`, 2026-05-16; verbatim quotes added 2026-05-23 (`stage1_cohort3_S901AS001AS002`) — sourced from chunk_24 (Ch7 §7.1 definitional and Figure 7.1) and chunk_38 (Appendix N net-transfer concept)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 24/35/38 + registry entry + project CLAUDE.md (AS-prefix framing mandate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
         <is>
           <t>- **Anu Framework stage**: Stage 3 INGESTION (cohort 1, failing chapters); ingestion gate IDs P31/P32</t>
         </is>
@@ -1405,7 +1521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1438,12 +1554,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Divide equation (1) by utilized capital K*.u: r'n = [1 - T/S* - Eu/S*][S*/(K*.u)] = (1-t-eu)r*' = (1-b)r*'. Where r*' = S*/(K*.u) = capacity utilization-adjusted Marxian rate of profit; r'n = Pn/(K*.u) = similarly adjusted NIPA-based net rate of profit; t = T/S* = tax share of surplus value; eu = Eu/S* = unproductive expenses share of surplus value; b = t + eu = social burden rate.</t>
+          <t>REVIEW 2026-07 (WP-E Group A) STUDY ANCHOR. Book Table 7.1 prints the social burden rate b = 1-(Pn/S*) directly, with its components Pn (profit-type income net of ALL taxes; Sources: Table 5.8) and S*. XS001-A is re-anchored to and now reproduces these printed b values (S505-A reproduces the book S* column exactly; Pn is sourced from Table 7.1). Prior XS001-A (0.79-0.86) used NIPA corporate profits as Pn, a wrong/narrower quantity.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994</t>
+          <t>ST 1994, Chapter 7, Table 7.1</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1571,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Observed net rate of profit r'n will fall relative to Marxian general rate r*' when greater proportion of surplus value absorbed in business taxes or unproductive expenses. Hence: b = social burden rate.</t>
+          <t>Divide equation (1) by utilized capital K*.u: r'n = [1 - T/S* - Eu/S*][S*/(K*.u)] = (1-t-eu)r*' = (1-b)r*'. Where r*' = S*/(K*.u) = capacity utilization-adjusted Marxian rate of profit; r'n = Pn/(K*.u) = similarly adjusted NIPA-based net rate of profit; t = T/S* = tax share of surplus value; eu = Eu/S* = unproductive expenses share of surplus value; b = t + eu = social burden rate.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1472,7 +1588,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Figure 7.1 shows the corresponding rise of 16% in social burden rate b over postwar period. Figure 7.2 result: NIPA-based rate rn falls substantially faster than Marxian rate. Marxian rate falls 25%, NIPA-based rate falls 39%.</t>
+          <t>Observed net rate of profit r'n will fall relative to Marxian general rate r*' when greater proportion of surplus value absorbed in business taxes or unproductive expenses. Hence: b = social burden rate.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1489,7 +1605,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Net transfer: NT = Benefits received by workers - Taxes paid by workers. Purpose: Measure net impact of state expenditures and taxes on standard of living of wage/salary earners. Finding: Net transfer is negative over most of 1952-85 period -&gt; net tax on workers.</t>
+          <t>Figure 7.1 shows the corresponding rise of 16% in social burden rate b over postwar period. Figure 7.2 result: NIPA-based rate rn falls substantially faster than Marxian rate. Marxian rate falls 25%, NIPA-based rate falls 39%.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1501,34 +1617,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>methodology_derived</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XS001 is a derived analytical series computing the Social Burden Rate. It is constructed from Net Social Wage (NSW, S607) and exploitation-related series. The social burden rate measures the proportion of surplus value absorbed by the net fiscal impact on workers — i.e., taxes paid by workers minus benefits and services received.</t>
+          <t>Net transfer: NT = Benefits received by workers - Taxes paid by workers. Purpose: Measure net impact of state expenditures and taxes on standard of living of wage/salary earners. Finding: Net transfer is negative over most of 1952-85 period -&gt; net tax on workers.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>series_registry.json (XS001 definition)</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>construction_reference</t>
+          <t>methodology_derived</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Registry describes XS001 as 'derived from NSW + exploitation series' with source_type 'analytical'. The legacy construction script is A07_social_burden_rate.py. Units are ratio. The series covers 1948-2024.</t>
+          <t>XS001 is a derived analytical series computing the Social Burden Rate. It is constructed from Net Social Wage (NSW, S607) and exploitation-related series. The social burden rate measures the proportion of surplus value absorbed by the net fiscal impact on workers — i.e., taxes paid by workers minus benefits and services received.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>series_registry.json</t>
+          <t>series_registry.json (XS001 definition)</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1656,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The social burden rate conceptually relates to Chapter 6's analysis of the net social wage (S607 = B_w + G_w - T_w) and its ratio to variable capital or surplus value. XS001 likely computes NSW relative to an exploitation measure (e.g., S*/V* or similar), quantifying the net fiscal redistribution burden on the surplus.</t>
+          <t>Registry describes XS001 as 'derived from NSW + exploitation series' with source_type 'analytical'. The legacy construction script is A07_social_burden_rate.py. Units are ratio. The series covers 1948-2024.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6 concepts; series_registry.json cross-references</t>
+          <t>series_registry.json</t>
         </is>
       </c>
     </row>
@@ -1557,33 +1673,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>The social burden rate conceptually relates to Chapter 6's analysis of the net social wage (S607 = B_w + G_w - T_w) and its ratio to variable capital or surplus value. XS001 likely computes NSW relative to an exploitation measure (e.g., S*/V* or similar), quantifying the net fiscal redistribution burden on the surplus.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6 concepts; series_registry.json cross-references</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>construction_reference</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Key input series: S607 (Net Social Wage), plus exploitation/surplus value series from Chapter 5 (e.g., S506 rate of surplus value, S505 surplus value). The construction array in the registry is empty, indicating this was handled by a standalone analytical script rather than the standard pipeline.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>series_registry.json</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>VERBATIM QUOTES (top-level)</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1599,7 +1723,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>213</t>
         </is>
       </c>
     </row>
@@ -1608,36 +1732,37 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>352-353</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>methodology_summary</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Derived analytical ratio measuring the social burden rate, computed from Net Social Wage (S607) and exploitation-related series. Legacy script: A07_social_burden_rate.py.</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Construction steps not specified in registry (empty array) — relies on legacy script</t>
         </is>
       </c>
     </row>
@@ -1645,23 +1770,23 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
+          <t>Construction steps not specified in registry (empty array) — relies on legacy script</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>Exact formula not yet verified against book text</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>S607</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1794,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S506</t>
+          <t>S607</t>
         </is>
       </c>
     </row>
@@ -1677,25 +1802,33 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
+          <t>S506</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>S505</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1779,7 +1912,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{"1948": 0.7906295851674003, "1958": 0.8287839156744095, "1970": 0.8425256084868625, "1980": 0.8474560743829904, "1989": 0.8577410093940578}</t>
+          <t>{"1948": 0.56, "1958": 0.62, "1970": 0.67, "1980": 0.66, "1989": 0.65}</t>
         </is>
       </c>
     </row>
